--- a/Excel/RingConfig.xlsx
+++ b/Excel/RingConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -71,7 +71,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>麻痹戒指</t>
+    <t>定身指环</t>
   </si>
   <si>
     <t>14,15,16,2001</t>
@@ -80,19 +80,19 @@
     <t>200,500,500,5</t>
   </si>
   <si>
-    <t>护身戒指</t>
+    <t>神盾指环</t>
   </si>
   <si>
     <t>14,15,16,2002</t>
   </si>
   <si>
-    <t>复活戒指</t>
+    <t>复生指环</t>
   </si>
   <si>
     <t>14,15,16,2003</t>
   </si>
   <si>
-    <t>防御戒指</t>
+    <t>护体指环</t>
   </si>
   <si>
     <t>14,15,16,2004</t>
@@ -101,22 +101,22 @@
     <t>护体神盾无需上阵，并且等级能额外增加20*戒指等级</t>
   </si>
   <si>
-    <t>传送神戒</t>
+    <t>破空指环</t>
   </si>
   <si>
     <t>14,15,16,2005</t>
   </si>
   <si>
-    <t>瞬息移动无需上阵，并且等级能额外增加20*戒指等级</t>
-  </si>
-  <si>
-    <t>隐身戒指</t>
+    <t>瞬息术无需上阵，并且等级能额外增加20*戒指等级</t>
+  </si>
+  <si>
+    <t>须弥指环</t>
   </si>
   <si>
     <t>14,15,16,2006</t>
   </si>
   <si>
-    <t>隐身术无需上阵，并且等级能额外增加20*戒指等级</t>
+    <t>隐身道法无需上阵，并且等级能额外增加20*戒指等级</t>
   </si>
 </sst>
 </file>
@@ -1231,7 +1231,7 @@
       <c r="G6" s="4">
         <v>1</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
@@ -1260,7 +1260,7 @@
       <c r="G7" s="4">
         <v>1</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="5" t="s">
@@ -1289,7 +1289,7 @@
       <c r="G8" s="4">
         <v>1</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="4" t="s">
         <v>19</v>
       </c>
       <c r="I8" s="5" t="s">
@@ -1318,7 +1318,7 @@
       <c r="G9" s="4">
         <v>20</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="4" t="s">
         <v>21</v>
       </c>
       <c r="I9" s="5" t="s">
@@ -1350,7 +1350,7 @@
       <c r="G10" s="4">
         <v>20</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I10" s="5" t="s">
@@ -1382,7 +1382,7 @@
       <c r="G11" s="4">
         <v>20</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I11" s="5" t="s">
@@ -1500,7 +1500,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 H3 I3 J3 K3 L3 D4 E4 F4 G4 H4 I4 J4 K4 L4 D5 E5 F5 G5 H5 I5 J5 K5 L5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/RingConfig.xlsx
+++ b/Excel/RingConfig.xlsx
@@ -98,7 +98,7 @@
     <t>14,15,16,2004</t>
   </si>
   <si>
-    <t>护体神盾无需上阵，并且等级能额外增加20*戒指等级</t>
+    <t>战吼无需上阵，并且等级能额外增加20*戒指等级</t>
   </si>
   <si>
     <t>破空指环</t>
@@ -107,7 +107,7 @@
     <t>14,15,16,2005</t>
   </si>
   <si>
-    <t>瞬息术无需上阵，并且等级能额外增加20*戒指等级</t>
+    <t>心灵传送无需上阵，并且等级能额外增加20*戒指等级</t>
   </si>
   <si>
     <t>须弥指环</t>

--- a/Excel/RingConfig.xlsx
+++ b/Excel/RingConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>Role</t>
+    <t>Type</t>
   </si>
   <si>
     <t>ItemId</t>
@@ -117,6 +117,45 @@
   </si>
   <si>
     <t>隐身道法无需上阵，并且等级能额外增加20*戒指等级</t>
+  </si>
+  <si>
+    <t>定身极戒</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2004,2013</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20</t>
+  </si>
+  <si>
+    <t>神盾极戒</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2005,2013</t>
+  </si>
+  <si>
+    <t>复生极戒</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2006,2013</t>
+  </si>
+  <si>
+    <t>护体极戒</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2007,2013</t>
+  </si>
+  <si>
+    <t>破空极戒</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2008,2013</t>
+  </si>
+  <si>
+    <t>须弥极戒</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2009,2013</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1130,7 @@
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="7" width="9.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="22.0833333333333" style="2" customWidth="1"/>
     <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
     <col min="11" max="11" width="15.625" style="2" customWidth="1"/>
     <col min="12" max="12" width="34.625" style="1" customWidth="1"/>
@@ -1099,14 +1138,14 @@
     <col min="16368" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="I2" s="2"/>
@@ -1215,7 +1254,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1244,7 +1283,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1273,7 +1312,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1302,7 +1341,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1334,7 +1373,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1366,7 +1405,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1398,109 +1437,253 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="5:7">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="5:7">
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="5:7">
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="5:7">
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="5:7">
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="5:7">
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="5:7">
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="5:7">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C13" s="1">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2</v>
+      </c>
+      <c r="E13" s="4">
+        <v>190007</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C14" s="1">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4">
+        <v>190008</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C15" s="1">
+        <v>9</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4">
+        <v>190009</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C16" s="1">
+        <v>10</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4">
+        <v>190010</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C17" s="1">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4">
+        <v>190011</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C18" s="1">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="4">
+        <v>190012</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="5:7">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="5:7">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="5:7">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="5:7">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="5:7">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="5:7">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="5:7">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="5:7">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="5:7">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="5:7">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="5:7">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="5:7">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L3 C4 D4 E4:L4 C5:L5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/RingConfig.xlsx
+++ b/Excel/RingConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="40">
   <si>
     <t>ID</t>
   </si>
@@ -122,40 +122,31 @@
     <t>定身极戒</t>
   </si>
   <si>
-    <t>2001,2002,2003,2004,2013</t>
-  </si>
-  <si>
-    <t>20,20,20,20,20</t>
+    <t>2001,2006,2007,2008,2010,91</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,1</t>
   </si>
   <si>
     <t>神盾极戒</t>
   </si>
   <si>
-    <t>2001,2002,2003,2005,2013</t>
+    <t>2001,2006,2007,2008,2010,92</t>
   </si>
   <si>
     <t>复生极戒</t>
   </si>
   <si>
-    <t>2001,2002,2003,2006,2013</t>
+    <t>2001,2006,2007,2008,2010,93</t>
   </si>
   <si>
     <t>护体极戒</t>
   </si>
   <si>
-    <t>2001,2002,2003,2007,2013</t>
-  </si>
-  <si>
     <t>破空极戒</t>
   </si>
   <si>
-    <t>2001,2002,2003,2008,2013</t>
-  </si>
-  <si>
     <t>须弥极戒</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,2009,2013</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1121,7 @@
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="7" width="9.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.0833333333333" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.4166666666667" style="2" customWidth="1"/>
     <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
     <col min="11" max="11" width="15.625" style="2" customWidth="1"/>
     <col min="12" max="12" width="34.625" style="1" customWidth="1"/>
@@ -1549,7 +1540,7 @@
         <v>37</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>32</v>
@@ -1575,10 +1566,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>32</v>
@@ -1604,10 +1595,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>32</v>
@@ -1683,7 +1674,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L3 C4 D4 E4:L4 C5:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/RingConfig.xlsx
+++ b/Excel/RingConfig.xlsx
@@ -122,22 +122,22 @@
     <t>定身极戒</t>
   </si>
   <si>
-    <t>2001,2006,2007,2008,2010,91</t>
-  </si>
-  <si>
-    <t>20,20,20,20,20,1</t>
+    <t>2001,2002,2003,2006,2007,2008,2010,91</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20,20,1</t>
   </si>
   <si>
     <t>神盾极戒</t>
   </si>
   <si>
-    <t>2001,2006,2007,2008,2010,92</t>
+    <t>2001,2002,2003,2006,2007,2008,2010,92</t>
   </si>
   <si>
     <t>复生极戒</t>
   </si>
   <si>
-    <t>2001,2006,2007,2008,2010,93</t>
+    <t>2001,2002,2003,2006,2007,2008,2010,93</t>
   </si>
   <si>
     <t>护体极戒</t>
@@ -1121,7 +1121,7 @@
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="7" width="9.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="23.4166666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.8333333333333" style="2" customWidth="1"/>
     <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
     <col min="11" max="11" width="15.625" style="2" customWidth="1"/>
     <col min="12" max="12" width="34.625" style="1" customWidth="1"/>

--- a/Excel/RingConfig.xlsx
+++ b/Excel/RingConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
@@ -122,7 +122,7 @@
     <t>定身极戒</t>
   </si>
   <si>
-    <t>2001,2002,2003,2006,2007,2008,2010,91</t>
+    <t>2001,2013,2003,2006,2007,2008,2010,91</t>
   </si>
   <si>
     <t>20,20,20,20,20,20,20,1</t>
@@ -131,22 +131,31 @@
     <t>神盾极戒</t>
   </si>
   <si>
-    <t>2001,2002,2003,2006,2007,2008,2010,92</t>
+    <t>2001,2013,2003,2006,2007,2008,2010,92</t>
   </si>
   <si>
     <t>复生极戒</t>
   </si>
   <si>
-    <t>2001,2002,2003,2006,2007,2008,2010,93</t>
+    <t>2001,2013,2003,2006,2007,2008,2010,93</t>
   </si>
   <si>
     <t>护体极戒</t>
   </si>
   <si>
+    <t>武力精通无需上阵，并且等级能额外增加100*戒指等级</t>
+  </si>
+  <si>
     <t>破空极戒</t>
   </si>
   <si>
+    <t>法力精通无需上阵，并且等级能额外增加100*戒指等级</t>
+  </si>
+  <si>
     <t>须弥极戒</t>
+  </si>
+  <si>
+    <t>道力精通无需上阵，并且等级能额外增加100*戒指等级</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1133,7 @@
     <col min="9" max="9" width="26.8333333333333" style="2" customWidth="1"/>
     <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
     <col min="11" max="11" width="15.625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="34.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="38.3333333333333" style="1" customWidth="1"/>
     <col min="13" max="16367" width="9" style="2"/>
     <col min="16368" max="16384" width="9" style="1"/>
   </cols>
@@ -1531,10 +1540,10 @@
         <v>190010</v>
       </c>
       <c r="F16" s="4">
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="G16" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>37</v>
@@ -1548,8 +1557,11 @@
       <c r="K16" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L16" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C17" s="1">
         <v>11</v>
       </c>
@@ -1560,13 +1572,13 @@
         <v>190011</v>
       </c>
       <c r="F17" s="4">
-        <v>0</v>
+        <v>2005</v>
       </c>
       <c r="G17" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>34</v>
@@ -1577,8 +1589,11 @@
       <c r="K17" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L17" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C18" s="1">
         <v>12</v>
       </c>
@@ -1589,13 +1604,13 @@
         <v>190012</v>
       </c>
       <c r="F18" s="4">
-        <v>0</v>
+        <v>3005</v>
       </c>
       <c r="G18" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>36</v>
@@ -1606,68 +1621,71 @@
       <c r="K18" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L18" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>

--- a/Excel/RingConfig.xlsx
+++ b/Excel/RingConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
   <si>
     <t>ID</t>
   </si>
@@ -44,6 +44,9 @@
     <t>RiseSkillLevel</t>
   </si>
   <si>
+    <t>RequireLevel</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -143,19 +146,19 @@
     <t>护体极戒</t>
   </si>
   <si>
-    <t>武力精通无需上阵，并且等级能额外增加100*戒指等级</t>
+    <t>武力精通增加100*戒指等级，极戒10级之后无需上阵</t>
   </si>
   <si>
     <t>破空极戒</t>
   </si>
   <si>
-    <t>法力精通无需上阵，并且等级能额外增加100*戒指等级</t>
+    <t>法力精通增加100*戒指等级，极戒10级之后无需上阵</t>
   </si>
   <si>
     <t>须弥极戒</t>
   </si>
   <si>
-    <t>道力精通无需上阵，并且等级能额外增加100*戒指等级</t>
+    <t>道力精通增加100*戒指等级，极戒10级之后无需上阵</t>
   </si>
 </sst>
 </file>
@@ -1123,36 +1126,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="7" width="9.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.8333333333333" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="15.625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="38.3333333333333" style="1" customWidth="1"/>
-    <col min="13" max="16367" width="9" style="2"/>
-    <col min="16368" max="16384" width="9" style="1"/>
+    <col min="8" max="8" width="15.3333333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.8333333333333" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="38.3333333333333" style="1" customWidth="1"/>
+    <col min="14" max="16368" width="9" style="2"/>
+    <col min="16369" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1185,12 +1189,15 @@
       <c r="L3" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1219,24 +1226,27 @@
       <c r="L4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>12</v>
@@ -1245,16 +1255,19 @@
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:12">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1270,20 +1283,23 @@
       <c r="G6" s="4">
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="5" t="s">
+      <c r="H6" s="4">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>17</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1299,20 +1315,23 @@
       <c r="G7" s="4">
         <v>1</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="4">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="L7" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1328,20 +1347,23 @@
       <c r="G8" s="4">
         <v>1</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="5" t="s">
+      <c r="H8" s="4">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>20</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>17</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1357,23 +1379,26 @@
       <c r="G9" s="4">
         <v>20</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="H9" s="4">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>17</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1389,23 +1414,26 @@
       <c r="G10" s="4">
         <v>20</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="5" t="s">
+      <c r="H10" s="4">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>25</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>17</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1421,28 +1449,32 @@
       <c r="G11" s="4">
         <v>20</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" s="5" t="s">
+      <c r="H11" s="4">
+        <v>1</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>28</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>17</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C13" s="1">
         <v>7</v>
       </c>
@@ -1458,20 +1490,23 @@
       <c r="G13" s="4">
         <v>0</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="5" t="s">
+      <c r="H13" s="4">
+        <v>10</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>31</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>33</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C14" s="1">
         <v>8</v>
       </c>
@@ -1487,20 +1522,23 @@
       <c r="G14" s="4">
         <v>0</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="4">
+        <v>10</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="L14" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C15" s="1">
         <v>9</v>
       </c>
@@ -1516,20 +1554,23 @@
       <c r="G15" s="4">
         <v>0</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="5" t="s">
+      <c r="H15" s="4">
+        <v>10</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>33</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C16" s="1">
         <v>10</v>
       </c>
@@ -1540,28 +1581,31 @@
         <v>190010</v>
       </c>
       <c r="F16" s="4">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="G16" s="4">
         <v>100</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>31</v>
+      <c r="H16" s="4">
+        <v>10</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>33</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C17" s="1">
         <v>11</v>
       </c>
@@ -1572,28 +1616,31 @@
         <v>190011</v>
       </c>
       <c r="F17" s="4">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="G17" s="4">
         <v>100</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>34</v>
+      <c r="H17" s="4">
+        <v>10</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>33</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C18" s="1">
         <v>12</v>
       </c>
@@ -1604,95 +1651,111 @@
         <v>190012</v>
       </c>
       <c r="F18" s="4">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="G18" s="4">
         <v>100</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>36</v>
+      <c r="H18" s="4">
+        <v>10</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>33</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3 H4 H5 C3:G5 I3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/RingConfig.xlsx
+++ b/Excel/RingConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="57">
   <si>
     <t>ID</t>
   </si>
@@ -131,34 +131,73 @@
     <t>20,20,20,20,20,20,20,1</t>
   </si>
   <si>
+    <t>武力精通增加150*戒指等级</t>
+  </si>
+  <si>
     <t>神盾极戒</t>
   </si>
   <si>
     <t>2001,2013,2003,2006,2007,2008,2010,92</t>
   </si>
   <si>
+    <t>法力精通增加150*戒指等级</t>
+  </si>
+  <si>
     <t>复生极戒</t>
   </si>
   <si>
     <t>2001,2013,2003,2006,2007,2008,2010,93</t>
   </si>
   <si>
+    <t>道力精通增加150*戒指等级</t>
+  </si>
+  <si>
     <t>护体极戒</t>
   </si>
   <si>
-    <t>武力精通增加100*戒指等级，极戒10级之后无需上阵</t>
+    <t>武力精通增加150*戒指等级，极戒10级之后无需上阵</t>
   </si>
   <si>
     <t>破空极戒</t>
   </si>
   <si>
-    <t>法力精通增加100*戒指等级，极戒10级之后无需上阵</t>
+    <t>法力精通增加150*戒指等级，极戒10级之后无需上阵</t>
   </si>
   <si>
     <t>须弥极戒</t>
   </si>
   <si>
-    <t>道力精通增加100*戒指等级，极戒10级之后无需上阵</t>
+    <t>道力精通增加150*戒指等级，极戒10级之后无需上阵</t>
+  </si>
+  <si>
+    <t>定身道戒</t>
+  </si>
+  <si>
+    <t>30,30,30,30,30,30,30,2</t>
+  </si>
+  <si>
+    <t>武神盾增加200*戒指等级</t>
+  </si>
+  <si>
+    <t>神盾道戒</t>
+  </si>
+  <si>
+    <t>法力盾增加200*戒指等级</t>
+  </si>
+  <si>
+    <t>复生道戒</t>
+  </si>
+  <si>
+    <t>道力盾增加200*戒指等级</t>
+  </si>
+  <si>
+    <t>护体道戒</t>
+  </si>
+  <si>
+    <t>破空道戒</t>
+  </si>
+  <si>
+    <t>须弥道戒</t>
   </si>
 </sst>
 </file>
@@ -1134,8 +1173,8 @@
     <col min="3" max="7" width="9.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.3333333333333" style="1" customWidth="1"/>
     <col min="9" max="9" width="12.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.8333333333333" style="2" customWidth="1"/>
-    <col min="11" max="11" width="15.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="29.3333333333333" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16.5833333333333" style="2" customWidth="1"/>
     <col min="12" max="12" width="15.625" style="2" customWidth="1"/>
     <col min="13" max="13" width="38.3333333333333" style="1" customWidth="1"/>
     <col min="14" max="16368" width="9" style="2"/>
@@ -1485,10 +1524,10 @@
         <v>190007</v>
       </c>
       <c r="F13" s="4">
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="G13" s="4">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H13" s="4">
         <v>10</v>
@@ -1504,6 +1543,9 @@
       </c>
       <c r="L13" s="5" t="s">
         <v>33</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -1517,25 +1559,28 @@
         <v>190008</v>
       </c>
       <c r="F14" s="4">
-        <v>0</v>
+        <v>2006</v>
       </c>
       <c r="G14" s="4">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H14" s="4">
         <v>10</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>33</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>33</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -1549,25 +1594,28 @@
         <v>190009</v>
       </c>
       <c r="F15" s="4">
-        <v>0</v>
+        <v>3006</v>
       </c>
       <c r="G15" s="4">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H15" s="4">
         <v>10</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>33</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>33</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -1584,13 +1632,13 @@
         <v>1006</v>
       </c>
       <c r="G16" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H16" s="4">
         <v>10</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>32</v>
@@ -1602,7 +1650,7 @@
         <v>33</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1619,16 +1667,16 @@
         <v>2006</v>
       </c>
       <c r="G17" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H17" s="4">
         <v>10</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>33</v>
@@ -1637,7 +1685,7 @@
         <v>33</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1654,16 +1702,16 @@
         <v>3006</v>
       </c>
       <c r="G18" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H18" s="4">
         <v>10</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>33</v>
@@ -1672,7 +1720,7 @@
         <v>33</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1682,40 +1730,214 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="C20" s="1">
+        <v>13</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3</v>
+      </c>
+      <c r="E20" s="4">
+        <v>190013</v>
+      </c>
+      <c r="F20" s="4">
+        <v>1005</v>
+      </c>
+      <c r="G20" s="4">
+        <v>200</v>
+      </c>
+      <c r="H20" s="4">
+        <v>20</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="C21" s="1">
+        <v>14</v>
+      </c>
+      <c r="D21" s="1">
+        <v>3</v>
+      </c>
+      <c r="E21" s="4">
+        <v>190014</v>
+      </c>
+      <c r="F21" s="4">
+        <v>2005</v>
+      </c>
+      <c r="G21" s="4">
+        <v>200</v>
+      </c>
+      <c r="H21" s="4">
+        <v>20</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="C22" s="1">
+        <v>15</v>
+      </c>
+      <c r="D22" s="1">
+        <v>3</v>
+      </c>
+      <c r="E22" s="4">
+        <v>190015</v>
+      </c>
+      <c r="F22" s="4">
+        <v>3005</v>
+      </c>
+      <c r="G22" s="4">
+        <v>200</v>
+      </c>
+      <c r="H22" s="4">
+        <v>20</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="C23" s="1">
+        <v>16</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3</v>
+      </c>
+      <c r="E23" s="4">
+        <v>190016</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1005</v>
+      </c>
+      <c r="G23" s="4">
+        <v>200</v>
+      </c>
+      <c r="H23" s="4">
+        <v>20</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
+      <c r="C24" s="1">
+        <v>17</v>
+      </c>
+      <c r="D24" s="1">
+        <v>3</v>
+      </c>
+      <c r="E24" s="4">
+        <v>190017</v>
+      </c>
+      <c r="F24" s="4">
+        <v>2005</v>
+      </c>
+      <c r="G24" s="4">
+        <v>200</v>
+      </c>
+      <c r="H24" s="4">
+        <v>20</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
+      <c r="C25" s="1">
+        <v>18</v>
+      </c>
+      <c r="D25" s="1">
+        <v>3</v>
+      </c>
+      <c r="E25" s="4">
+        <v>190018</v>
+      </c>
+      <c r="F25" s="4">
+        <v>3005</v>
+      </c>
+      <c r="G25" s="4">
+        <v>200</v>
+      </c>
+      <c r="H25" s="4">
+        <v>20</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E26" s="4"/>
@@ -1755,7 +1977,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3 H4 H5 C3:G5 I3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
